--- a/Complete_LOG.xlsx
+++ b/Complete_LOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main_IMN\MSF_IMN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30910AFE-5282-407C-95F5-B2F2A1239449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EE211-AE28-4670-929C-9C7E3544BDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
   <si>
     <t>Training data folder</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>GAT</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
 </sst>
 </file>
@@ -1049,10 +1052,16 @@
         <v>300</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="J11" s="1">
+        <v>21</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="M11" s="3">
+        <v>8.3333333333333329E-2</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="4">
         <v>301</v>
@@ -1565,13 +1574,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="P3:P6"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="P7:P10"/>
     <mergeCell ref="P11:P14"/>
     <mergeCell ref="P15:P18"/>
-    <mergeCell ref="P3:P6"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
